--- a/healthcare_forms/001_water_safety_survey--healthcare_forms.xlsx
+++ b/healthcare_forms/001_water_safety_survey--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'lifeguard'}</t>
+          <t>lifeguard</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Lifeguard'}</t>
+          <t>Lifeguard</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'scuba_diver'}</t>
+          <t>scuba_diver</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Scuba diver'}</t>
+          <t>Scuba diver</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'boat_operator'}</t>
+          <t>boat_operator</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Boat operator'}</t>
+          <t>Boat operator</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'teacher'}</t>
+          <t>teacher</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Teacher'}</t>
+          <t>Teacher</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'cpr'}</t>
+          <t>cpr</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'CPR'}</t>
+          <t>CPR</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'first_aid'}</t>
+          <t>first_aid</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'First aid'}</t>
+          <t>First aid</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'lifesaving'}</t>
+          <t>lifesaving</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Lifesaving'}</t>
+          <t>Lifesaving</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'strong_current'}</t>
+          <t>strong_current</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Strong current'}</t>
+          <t>Strong current</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'steep_drop'}</t>
+          <t>steep_drop</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Steep drop'}</t>
+          <t>Steep drop</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'underwater_hazard'}</t>
+          <t>underwater_hazard</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Underwater hazard'}</t>
+          <t>Underwater hazard</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'floating'}</t>
+          <t>floating</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Floating'}</t>
+          <t>Floating</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'swimming_rescue'}</t>
+          <t>swimming_rescue</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Swimming rescue'}</t>
+          <t>Swimming rescue</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'boating_rescue'}</t>
+          <t>boating_rescue</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Boating rescue'}</t>
+          <t>Boating rescue</t>
         </is>
       </c>
     </row>
